--- a/data/rugvista_bestsellers.xlsx
+++ b/data/rugvista_bestsellers.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C347"/>
+  <dimension ref="A1:C348"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -4933,6 +4933,19 @@
         <v>2144.21</v>
       </c>
     </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B348" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C348" t="n">
+        <v>2175.36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_bestsellers.xlsx
+++ b/data/rugvista_bestsellers.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C348"/>
+  <dimension ref="A1:C349"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -4946,6 +4946,19 @@
         <v>2175.36</v>
       </c>
     </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B349" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C349" t="n">
+        <v>2189.73</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_bestsellers.xlsx
+++ b/data/rugvista_bestsellers.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C349"/>
+  <dimension ref="A1:C350"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -4959,6 +4959,19 @@
         <v>2189.73</v>
       </c>
     </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B350" t="n">
+        <v>2150</v>
+      </c>
+      <c r="C350" t="n">
+        <v>2200.62</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_bestsellers.xlsx
+++ b/data/rugvista_bestsellers.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C350"/>
+  <dimension ref="A1:C351"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -4972,6 +4972,19 @@
         <v>2200.62</v>
       </c>
     </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B351" t="n">
+        <v>2100</v>
+      </c>
+      <c r="C351" t="n">
+        <v>2190.97</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_bestsellers.xlsx
+++ b/data/rugvista_bestsellers.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C351"/>
+  <dimension ref="A1:C352"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -4985,6 +4985,19 @@
         <v>2190.97</v>
       </c>
     </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B352" t="n">
+        <v>2100</v>
+      </c>
+      <c r="C352" t="n">
+        <v>2176.67</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_bestsellers.xlsx
+++ b/data/rugvista_bestsellers.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C352"/>
+  <dimension ref="A1:C353"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -4998,6 +4998,19 @@
         <v>2176.67</v>
       </c>
     </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C353" t="n">
+        <v>2175.64</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_bestsellers.xlsx
+++ b/data/rugvista_bestsellers.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C353"/>
+  <dimension ref="A1:C354"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5011,6 +5011,19 @@
         <v>2175.64</v>
       </c>
     </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C354" t="n">
+        <v>2177.54</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_bestsellers.xlsx
+++ b/data/rugvista_bestsellers.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C354"/>
+  <dimension ref="A1:C355"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5024,6 +5024,19 @@
         <v>2177.54</v>
       </c>
     </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C355" t="n">
+        <v>2205.65</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_bestsellers.xlsx
+++ b/data/rugvista_bestsellers.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C355"/>
+  <dimension ref="A1:C356"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5037,6 +5037,19 @@
         <v>2205.65</v>
       </c>
     </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C356" t="n">
+        <v>2213.45</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_bestsellers.xlsx
+++ b/data/rugvista_bestsellers.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C356"/>
+  <dimension ref="A1:C357"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5050,6 +5050,19 @@
         <v>2213.45</v>
       </c>
     </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>2150</v>
+      </c>
+      <c r="C357" t="n">
+        <v>2211.93</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_bestsellers.xlsx
+++ b/data/rugvista_bestsellers.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C357"/>
+  <dimension ref="A1:C358"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5063,6 +5063,19 @@
         <v>2211.93</v>
       </c>
     </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>2200</v>
+      </c>
+      <c r="C358" t="n">
+        <v>2215.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_bestsellers.xlsx
+++ b/data/rugvista_bestsellers.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C358"/>
+  <dimension ref="A1:C359"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5076,6 +5076,19 @@
         <v>2215.3</v>
       </c>
     </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>2200</v>
+      </c>
+      <c r="C359" t="n">
+        <v>2263.68</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_bestsellers.xlsx
+++ b/data/rugvista_bestsellers.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C359"/>
+  <dimension ref="A1:C360"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5089,6 +5089,19 @@
         <v>2263.68</v>
       </c>
     </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>2200</v>
+      </c>
+      <c r="C360" t="n">
+        <v>2262.17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_bestsellers.xlsx
+++ b/data/rugvista_bestsellers.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C360"/>
+  <dimension ref="A1:C361"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5102,6 +5102,19 @@
         <v>2262.17</v>
       </c>
     </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B361" t="n">
+        <v>2200</v>
+      </c>
+      <c r="C361" t="n">
+        <v>2269.58</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_bestsellers.xlsx
+++ b/data/rugvista_bestsellers.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C361"/>
+  <dimension ref="A1:C362"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5115,6 +5115,19 @@
         <v>2269.58</v>
       </c>
     </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
+        <v>2200</v>
+      </c>
+      <c r="C362" t="n">
+        <v>2258.05</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_bestsellers.xlsx
+++ b/data/rugvista_bestsellers.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C362"/>
+  <dimension ref="A1:C363"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5128,6 +5128,19 @@
         <v>2258.05</v>
       </c>
     </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B363" t="n">
+        <v>2200</v>
+      </c>
+      <c r="C363" t="n">
+        <v>2247.76</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_bestsellers.xlsx
+++ b/data/rugvista_bestsellers.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C363"/>
+  <dimension ref="A1:C364"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5141,6 +5141,19 @@
         <v>2247.76</v>
       </c>
     </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B364" t="n">
+        <v>2200</v>
+      </c>
+      <c r="C364" t="n">
+        <v>2226.21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_bestsellers.xlsx
+++ b/data/rugvista_bestsellers.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C364"/>
+  <dimension ref="A1:C365"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5154,6 +5154,19 @@
         <v>2226.21</v>
       </c>
     </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B365" t="n">
+        <v>2150</v>
+      </c>
+      <c r="C365" t="n">
+        <v>2218.77</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_bestsellers.xlsx
+++ b/data/rugvista_bestsellers.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C365"/>
+  <dimension ref="A1:C366"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5167,6 +5167,19 @@
         <v>2218.77</v>
       </c>
     </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B366" t="n">
+        <v>2100</v>
+      </c>
+      <c r="C366" t="n">
+        <v>2203.68</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_bestsellers.xlsx
+++ b/data/rugvista_bestsellers.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C366"/>
+  <dimension ref="A1:C367"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5180,6 +5180,19 @@
         <v>2203.68</v>
       </c>
     </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B367" t="n">
+        <v>2100</v>
+      </c>
+      <c r="C367" t="n">
+        <v>2180.6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_bestsellers.xlsx
+++ b/data/rugvista_bestsellers.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C367"/>
+  <dimension ref="A1:C368"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5193,6 +5193,19 @@
         <v>2180.6</v>
       </c>
     </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B368" t="n">
+        <v>2100</v>
+      </c>
+      <c r="C368" t="n">
+        <v>2205.29</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_bestsellers.xlsx
+++ b/data/rugvista_bestsellers.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C368"/>
+  <dimension ref="A1:C369"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5206,6 +5206,19 @@
         <v>2205.29</v>
       </c>
     </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B369" t="n">
+        <v>2100</v>
+      </c>
+      <c r="C369" t="n">
+        <v>2206.97</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_bestsellers.xlsx
+++ b/data/rugvista_bestsellers.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C369"/>
+  <dimension ref="A1:C370"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5219,6 +5219,19 @@
         <v>2206.97</v>
       </c>
     </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B370" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C370" t="n">
+        <v>2202.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_bestsellers.xlsx
+++ b/data/rugvista_bestsellers.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C370"/>
+  <dimension ref="A1:C371"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5232,6 +5232,19 @@
         <v>2202.8</v>
       </c>
     </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B371" t="n">
+        <v>1900</v>
+      </c>
+      <c r="C371" t="n">
+        <v>2141.04</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_bestsellers.xlsx
+++ b/data/rugvista_bestsellers.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C371"/>
+  <dimension ref="A1:C372"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5245,6 +5245,19 @@
         <v>2141.04</v>
       </c>
     </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B372" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C372" t="n">
+        <v>2199.57</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_bestsellers.xlsx
+++ b/data/rugvista_bestsellers.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C372"/>
+  <dimension ref="A1:C373"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5258,6 +5258,19 @@
         <v>2199.57</v>
       </c>
     </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B373" t="n">
+        <v>2170</v>
+      </c>
+      <c r="C373" t="n">
+        <v>2288.07</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_bestsellers.xlsx
+++ b/data/rugvista_bestsellers.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C373"/>
+  <dimension ref="A1:C374"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5271,6 +5271,19 @@
         <v>2288.07</v>
       </c>
     </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B374" t="n">
+        <v>2200</v>
+      </c>
+      <c r="C374" t="n">
+        <v>2344.17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_bestsellers.xlsx
+++ b/data/rugvista_bestsellers.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C374"/>
+  <dimension ref="A1:C375"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5284,6 +5284,19 @@
         <v>2344.17</v>
       </c>
     </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B375" t="n">
+        <v>2200</v>
+      </c>
+      <c r="C375" t="n">
+        <v>2342.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_bestsellers.xlsx
+++ b/data/rugvista_bestsellers.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C375"/>
+  <dimension ref="A1:C376"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5297,6 +5297,19 @@
         <v>2342.2</v>
       </c>
     </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B376" t="n">
+        <v>2200</v>
+      </c>
+      <c r="C376" t="n">
+        <v>2354.45</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_bestsellers.xlsx
+++ b/data/rugvista_bestsellers.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C376"/>
+  <dimension ref="A1:C377"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5310,6 +5310,19 @@
         <v>2354.45</v>
       </c>
     </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B377" t="n">
+        <v>2100</v>
+      </c>
+      <c r="C377" t="n">
+        <v>2317.15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_bestsellers.xlsx
+++ b/data/rugvista_bestsellers.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C377"/>
+  <dimension ref="A1:C378"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5323,6 +5323,19 @@
         <v>2317.15</v>
       </c>
     </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B378" t="n">
+        <v>2135</v>
+      </c>
+      <c r="C378" t="n">
+        <v>2300.51</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_bestsellers.xlsx
+++ b/data/rugvista_bestsellers.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C378"/>
+  <dimension ref="A1:C379"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5336,6 +5336,19 @@
         <v>2300.51</v>
       </c>
     </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B379" t="n">
+        <v>2100</v>
+      </c>
+      <c r="C379" t="n">
+        <v>2277.48</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_bestsellers.xlsx
+++ b/data/rugvista_bestsellers.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C379"/>
+  <dimension ref="A1:C380"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5349,6 +5349,19 @@
         <v>2277.48</v>
       </c>
     </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B380" t="n">
+        <v>2400</v>
+      </c>
+      <c r="C380" t="n">
+        <v>2430.41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_bestsellers.xlsx
+++ b/data/rugvista_bestsellers.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C380"/>
+  <dimension ref="A1:C381"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5362,6 +5362,19 @@
         <v>2430.41</v>
       </c>
     </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B381" t="n">
+        <v>2185</v>
+      </c>
+      <c r="C381" t="n">
+        <v>2300.08</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_bestsellers.xlsx
+++ b/data/rugvista_bestsellers.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C381"/>
+  <dimension ref="A1:C382"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5375,6 +5375,19 @@
         <v>2300.08</v>
       </c>
     </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B382" t="n">
+        <v>2200</v>
+      </c>
+      <c r="C382" t="n">
+        <v>2310.34</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_bestsellers.xlsx
+++ b/data/rugvista_bestsellers.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C382"/>
+  <dimension ref="A1:C383"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5388,6 +5388,19 @@
         <v>2310.34</v>
       </c>
     </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B383" t="n">
+        <v>2170</v>
+      </c>
+      <c r="C383" t="n">
+        <v>2318.57</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_bestsellers.xlsx
+++ b/data/rugvista_bestsellers.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C383"/>
+  <dimension ref="A1:C384"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5401,6 +5401,19 @@
         <v>2318.57</v>
       </c>
     </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B384" t="n">
+        <v>2100</v>
+      </c>
+      <c r="C384" t="n">
+        <v>2307.04</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_bestsellers.xlsx
+++ b/data/rugvista_bestsellers.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C384"/>
+  <dimension ref="A1:C385"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5414,6 +5414,19 @@
         <v>2307.04</v>
       </c>
     </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B385" t="n">
+        <v>2185</v>
+      </c>
+      <c r="C385" t="n">
+        <v>2304.56</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_bestsellers.xlsx
+++ b/data/rugvista_bestsellers.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C385"/>
+  <dimension ref="A1:C386"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5427,6 +5427,19 @@
         <v>2304.56</v>
       </c>
     </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B386" t="n">
+        <v>2200</v>
+      </c>
+      <c r="C386" t="n">
+        <v>2322.87</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_bestsellers.xlsx
+++ b/data/rugvista_bestsellers.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C386"/>
+  <dimension ref="A1:C387"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5440,6 +5440,19 @@
         <v>2322.87</v>
       </c>
     </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B387" t="n">
+        <v>2250</v>
+      </c>
+      <c r="C387" t="n">
+        <v>2330.86</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_bestsellers.xlsx
+++ b/data/rugvista_bestsellers.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C387"/>
+  <dimension ref="A1:C388"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5453,6 +5453,19 @@
         <v>2330.86</v>
       </c>
     </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B388" t="n">
+        <v>2300</v>
+      </c>
+      <c r="C388" t="n">
+        <v>2320.34</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_bestsellers.xlsx
+++ b/data/rugvista_bestsellers.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C388"/>
+  <dimension ref="A1:C391"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5466,6 +5466,45 @@
         <v>2320.34</v>
       </c>
     </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B389" t="n">
+        <v>2250</v>
+      </c>
+      <c r="C389" t="n">
+        <v>2262.54</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B390" t="n">
+        <v>2200</v>
+      </c>
+      <c r="C390" t="n">
+        <v>2263.39</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B391" t="n">
+        <v>2100</v>
+      </c>
+      <c r="C391" t="n">
+        <v>2233.33</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_bestsellers.xlsx
+++ b/data/rugvista_bestsellers.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C391"/>
+  <dimension ref="A1:C392"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5505,6 +5505,19 @@
         <v>2233.33</v>
       </c>
     </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B392" t="n">
+        <v>2135</v>
+      </c>
+      <c r="C392" t="n">
+        <v>2231.75</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_bestsellers.xlsx
+++ b/data/rugvista_bestsellers.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C392"/>
+  <dimension ref="A1:C393"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5518,6 +5518,19 @@
         <v>2231.75</v>
       </c>
     </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B393" t="n">
+        <v>2200</v>
+      </c>
+      <c r="C393" t="n">
+        <v>2248.26</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_bestsellers.xlsx
+++ b/data/rugvista_bestsellers.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C393"/>
+  <dimension ref="A1:C394"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5531,6 +5531,19 @@
         <v>2248.26</v>
       </c>
     </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B394" t="n">
+        <v>2200</v>
+      </c>
+      <c r="C394" t="n">
+        <v>2298.71</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_bestsellers.xlsx
+++ b/data/rugvista_bestsellers.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C394"/>
+  <dimension ref="A1:C395"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5544,6 +5544,19 @@
         <v>2298.71</v>
       </c>
     </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B395" t="n">
+        <v>2200</v>
+      </c>
+      <c r="C395" t="n">
+        <v>2293.28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_bestsellers.xlsx
+++ b/data/rugvista_bestsellers.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C395"/>
+  <dimension ref="A1:C396"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5557,6 +5557,19 @@
         <v>2293.28</v>
       </c>
     </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B396" t="n">
+        <v>2080</v>
+      </c>
+      <c r="C396" t="n">
+        <v>2157.54</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
